--- a/差异化城市设计/计算-蓄电池-拉萨.xlsx
+++ b/差异化城市设计/计算-蓄电池-拉萨.xlsx
@@ -939,9 +939,10 @@
           <t>E_bat,min 最低标称能量</t>
         </is>
       </c>
-      <c r="B2" s="4">
-        <f>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*K_T)</f>
-        <v/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*K_T)</t>
+        </is>
       </c>
       <c r="C2">
         <f>参数!B2*参数!B3*参数!B4/(参数!B5*参数!B6*参数!B7*参数!B8)</f>
@@ -959,9 +960,10 @@
           <t>C_bat,min 安时</t>
         </is>
       </c>
-      <c r="B3" s="4">
-        <f>1000*E_bat,min/V_nom</f>
-        <v/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>1000*E_bat,min/V_nom</t>
+        </is>
       </c>
       <c r="C3">
         <f>ROUND(1000*C2/参数!B9,1)</f>
@@ -979,9 +981,10 @@
           <t>N_P,E 并联数量(能量)</t>
         </is>
       </c>
-      <c r="B4">
-        <f>CEILING(E_bat,min/E_mod,1)</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CEILING(E_bat,min/E_mod,1)</t>
+        </is>
       </c>
       <c r="C4">
         <f>CEILING(C2/参数!B10,1)</f>
@@ -999,9 +1002,10 @@
           <t>E_actual 实际标称能量</t>
         </is>
       </c>
-      <c r="B5">
-        <f>N_P*E_mod</f>
-        <v/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N_P*E_mod</t>
+        </is>
       </c>
       <c r="C5">
         <f>C4*参数!B10</f>
@@ -1019,9 +1023,10 @@
           <t>实际/下限比值</t>
         </is>
       </c>
-      <c r="B6">
-        <f>E_actual/E_bat,min</f>
-        <v/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E_actual/E_bat,min</t>
+        </is>
       </c>
       <c r="C6">
         <f>C5/C2</f>
@@ -1033,21 +1038,17 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>敏感性：3 d 自主供电</t>
         </is>
       </c>
-      <c r="B8">
-        <f>E_AC*3*K_R/(DOD*eta_dis*eta_inv*K_T)</f>
-        <v/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E_AC*3*K_R/(DOD*eta_dis*eta_inv*K_T)</t>
+        </is>
       </c>
       <c r="C8">
         <f>参数!B2*3*参数!B4/(参数!B5*参数!B6*参数!B7*参数!B8)</f>
@@ -1085,9 +1086,10 @@
           <t>E_actual(3d)</t>
         </is>
       </c>
-      <c r="B10">
-        <f>N_P3d*E_mod</f>
-        <v/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N_P3d*E_mod</t>
+        </is>
       </c>
       <c r="C10">
         <f>C9*参数!B10</f>
@@ -1099,21 +1101,17 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>敏感性：DOD=0.80 保守</t>
         </is>
       </c>
-      <c r="B12">
-        <f>E_AC*N_A*K_R/(0.8*eta_dis*eta_inv*K_T)</f>
-        <v/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E_AC*N_A*K_R/(0.8*eta_dis*eta_inv*K_T)</t>
+        </is>
       </c>
       <c r="C12">
         <f>参数!B2*参数!B3*参数!B4/(0.8*参数!B6*参数!B7*参数!B8)</f>
@@ -1145,21 +1143,17 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>敏感性：设备间不保温 K_T=0.70</t>
         </is>
       </c>
-      <c r="B15">
-        <f>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*0.7)</f>
-        <v/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*0.7)</t>
+        </is>
       </c>
       <c r="C15">
         <f>参数!B2*参数!B3*参数!B4/(参数!B5*参数!B6*参数!B7*0.7)</f>
@@ -1177,9 +1171,10 @@
           <t>N_P(K_T=0.70)</t>
         </is>
       </c>
-      <c r="B16">
-        <f>CEILING(Ekt/E_mod,1)</f>
-        <v/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CEILING(Ekt/E_mod,1)</t>
+        </is>
       </c>
       <c r="C16">
         <f>CEILING(C14/参数!B10,1)</f>
@@ -1280,13 +1275,15 @@
           <t>连续放电电流 I_dis</t>
         </is>
       </c>
-      <c r="B4">
-        <f>ROUND(P_inv_r/(V_bat_min*eta_inv),1)</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>5*100 A</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ROUND(P_inv_r/(V_bat_min*eta_inv),1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5*100 A</t>
+        </is>
       </c>
       <c r="D4">
         <f>IF(ROUND(参数!B12/(参数!B13*参数!B7),1)&lt;=500,"OK","FAIL")</f>
@@ -1299,9 +1296,10 @@
           <t>短时放电电流 I_dis,sur</t>
         </is>
       </c>
-      <c r="B5">
-        <f>ROUND(P_short/(V_bat_min*eta_inv),1)</f>
-        <v/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ROUND(P_short/(V_bat_min*eta_inv),1)</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1319,9 +1317,10 @@
           <t>最大充电电流 I_chg</t>
         </is>
       </c>
-      <c r="B6">
-        <f>ROUND(MIN(P_PV*eta_MPPT/V_bat_chg,I_ctrl_out_max),1)</f>
-        <v/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ROUND(MIN(P_PV*eta_MPPT/V_bat_chg,I_ctrl_out_max),1)</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
